--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260813.xlsx
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>30,987,000</t>
+          <t>35,274,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>35,274,000</t>
+          <t>30,987,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>2,169,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,169,000</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>2,660,185,322</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,660,185,322</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,498,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>3,498,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
